--- a/docs/build/lakeshore-enterprise-context/source/04_finance_performance/pnl_baseline.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/04_finance_performance/pnl_baseline.xlsx
@@ -532,40 +532,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2292.3</v>
+        <v>2634.5</v>
       </c>
       <c r="C3" t="n">
-        <v>7136.4</v>
+        <v>6495.8</v>
       </c>
       <c r="D3" t="n">
-        <v>6709.6</v>
+        <v>299.1</v>
       </c>
       <c r="E3" t="n">
-        <v>4297.8</v>
+        <v>6093</v>
       </c>
       <c r="F3" t="n">
-        <v>3284.5</v>
+        <v>2005.8</v>
       </c>
       <c r="G3" t="n">
-        <v>845.4</v>
+        <v>3871.4</v>
       </c>
       <c r="H3" t="n">
-        <v>7511.8</v>
+        <v>1517.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2993.3</v>
+        <v>110.3</v>
       </c>
       <c r="J3" t="n">
-        <v>6936.4</v>
+        <v>4427.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3709.5</v>
+        <v>534.9</v>
       </c>
       <c r="L3" t="n">
-        <v>3130.3</v>
+        <v>3225.1</v>
       </c>
       <c r="M3" t="n">
-        <v>4193.8</v>
+        <v>4240.8</v>
       </c>
     </row>
     <row r="4">
@@ -575,40 +575,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1055.5</v>
+        <v>5213.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4839.7</v>
+        <v>3592.6</v>
       </c>
       <c r="D4" t="n">
-        <v>5245.9</v>
+        <v>7074.9</v>
       </c>
       <c r="E4" t="n">
-        <v>3299.3</v>
+        <v>6029.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1779.5</v>
+        <v>568.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5311.3</v>
+        <v>5939.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3173.7</v>
+        <v>3567.9</v>
       </c>
       <c r="I4" t="n">
-        <v>6653.9</v>
+        <v>1679.2</v>
       </c>
       <c r="J4" t="n">
-        <v>6736.7</v>
+        <v>6965.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3414.3</v>
+        <v>6644.3</v>
       </c>
       <c r="L4" t="n">
-        <v>6944.1</v>
+        <v>2292.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1539.9</v>
+        <v>7136.4</v>
       </c>
     </row>
     <row r="5">
@@ -618,40 +618,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2756.1</v>
+        <v>6709.6</v>
       </c>
       <c r="C5" t="n">
-        <v>3882.8</v>
+        <v>4297.8</v>
       </c>
       <c r="D5" t="n">
-        <v>606.6</v>
+        <v>3284.5</v>
       </c>
       <c r="E5" t="n">
-        <v>6520.7</v>
+        <v>845.4</v>
       </c>
       <c r="F5" t="n">
-        <v>194.3</v>
+        <v>7511.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1426</v>
+        <v>2993.3</v>
       </c>
       <c r="H5" t="n">
-        <v>4098.7</v>
+        <v>6936.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7703.5</v>
+        <v>3709.5</v>
       </c>
       <c r="J5" t="n">
-        <v>6351.7</v>
+        <v>3130.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3344.1</v>
+        <v>4193.8</v>
       </c>
       <c r="L5" t="n">
-        <v>4738.6</v>
+        <v>1055.5</v>
       </c>
       <c r="M5" t="n">
-        <v>526.4</v>
+        <v>4839.7</v>
       </c>
     </row>
     <row r="6">
@@ -661,40 +661,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6636.2</v>
+        <v>5245.9</v>
       </c>
       <c r="C6" t="n">
-        <v>4537.1</v>
+        <v>3299.3</v>
       </c>
       <c r="D6" t="n">
-        <v>6066.4</v>
+        <v>1779.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3891.8</v>
+        <v>5311.3</v>
       </c>
       <c r="F6" t="n">
-        <v>3531.8</v>
+        <v>3173.7</v>
       </c>
       <c r="G6" t="n">
-        <v>7458.2</v>
+        <v>6653.9</v>
       </c>
       <c r="H6" t="n">
-        <v>3478.3</v>
+        <v>6736.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4007.4</v>
+        <v>3414.3</v>
       </c>
       <c r="J6" t="n">
-        <v>5026</v>
+        <v>6944.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4474.7</v>
+        <v>1539.9</v>
       </c>
       <c r="L6" t="n">
-        <v>416.4</v>
+        <v>2756.1</v>
       </c>
       <c r="M6" t="n">
-        <v>1960.7</v>
+        <v>3882.8</v>
       </c>
     </row>
     <row r="7">
@@ -704,40 +704,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2415.8</v>
+        <v>606.6</v>
       </c>
       <c r="C7" t="n">
-        <v>4308.1</v>
+        <v>6520.7</v>
       </c>
       <c r="D7" t="n">
-        <v>870.5</v>
+        <v>194.3</v>
       </c>
       <c r="E7" t="n">
-        <v>3266.2</v>
+        <v>1426</v>
       </c>
       <c r="F7" t="n">
-        <v>6911.5</v>
+        <v>4098.7</v>
       </c>
       <c r="G7" t="n">
-        <v>7933</v>
+        <v>7703.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1161.8</v>
+        <v>6351.7</v>
       </c>
       <c r="I7" t="n">
-        <v>4231.5</v>
+        <v>3344.1</v>
       </c>
       <c r="J7" t="n">
-        <v>8069</v>
+        <v>4738.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4552.4</v>
+        <v>526.4</v>
       </c>
       <c r="L7" t="n">
-        <v>4506.3</v>
+        <v>6636.2</v>
       </c>
       <c r="M7" t="n">
-        <v>8379</v>
+        <v>4537.1</v>
       </c>
     </row>
     <row r="8">
@@ -747,40 +747,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3030</v>
+        <v>6066.4</v>
       </c>
       <c r="C8" t="n">
-        <v>5985.2</v>
+        <v>3891.8</v>
       </c>
       <c r="D8" t="n">
-        <v>4271.8</v>
+        <v>3531.8</v>
       </c>
       <c r="E8" t="n">
-        <v>1716.7</v>
+        <v>7458.2</v>
       </c>
       <c r="F8" t="n">
-        <v>7401.6</v>
+        <v>3478.3</v>
       </c>
       <c r="G8" t="n">
-        <v>5149.1</v>
+        <v>4007.4</v>
       </c>
       <c r="H8" t="n">
-        <v>2709.7</v>
+        <v>5026</v>
       </c>
       <c r="I8" t="n">
-        <v>3795.3</v>
+        <v>4474.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1159.2</v>
+        <v>416.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2982.3</v>
+        <v>1960.7</v>
       </c>
       <c r="L8" t="n">
-        <v>3825.6</v>
+        <v>2415.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3002.8</v>
+        <v>4308.1</v>
       </c>
     </row>
     <row r="9">
@@ -790,40 +790,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3394.2</v>
+        <v>870.5</v>
       </c>
       <c r="C9" t="n">
-        <v>2041.1</v>
+        <v>3266.2</v>
       </c>
       <c r="D9" t="n">
-        <v>3997.3</v>
+        <v>6911.5</v>
       </c>
       <c r="E9" t="n">
-        <v>4745.3</v>
+        <v>7933</v>
       </c>
       <c r="F9" t="n">
-        <v>4955</v>
+        <v>1161.8</v>
       </c>
       <c r="G9" t="n">
-        <v>3572.9</v>
+        <v>4231.5</v>
       </c>
       <c r="H9" t="n">
-        <v>474.7</v>
+        <v>8069</v>
       </c>
       <c r="I9" t="n">
-        <v>3808.1</v>
+        <v>4552.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2025</v>
+        <v>4506.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1670.8</v>
+        <v>8379</v>
       </c>
       <c r="L9" t="n">
-        <v>6368.3</v>
+        <v>3030</v>
       </c>
       <c r="M9" t="n">
-        <v>3991</v>
+        <v>5985.2</v>
       </c>
     </row>
     <row r="10">
@@ -833,40 +833,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5194.9</v>
+        <v>4271.8</v>
       </c>
       <c r="C10" t="n">
-        <v>7545.9</v>
+        <v>1716.7</v>
       </c>
       <c r="D10" t="n">
-        <v>4207.2</v>
+        <v>7401.6</v>
       </c>
       <c r="E10" t="n">
-        <v>2028.7</v>
+        <v>5149.1</v>
       </c>
       <c r="F10" t="n">
-        <v>7602.4</v>
+        <v>2709.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4602.1</v>
+        <v>3795.3</v>
       </c>
       <c r="H10" t="n">
-        <v>6303.8</v>
+        <v>1159.2</v>
       </c>
       <c r="I10" t="n">
-        <v>6832.5</v>
+        <v>2982.3</v>
       </c>
       <c r="J10" t="n">
-        <v>5774.2</v>
+        <v>3825.6</v>
       </c>
       <c r="K10" t="n">
-        <v>7838.8</v>
+        <v>3002.8</v>
       </c>
       <c r="L10" t="n">
-        <v>4018.2</v>
+        <v>3394.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1925.4</v>
+        <v>2041.1</v>
       </c>
     </row>
     <row r="11">
@@ -876,40 +876,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3392.8</v>
+        <v>3997.3</v>
       </c>
       <c r="C11" t="n">
-        <v>213.6</v>
+        <v>4745.3</v>
       </c>
       <c r="D11" t="n">
-        <v>4698.9</v>
+        <v>4955</v>
       </c>
       <c r="E11" t="n">
-        <v>5577.4</v>
+        <v>3572.9</v>
       </c>
       <c r="F11" t="n">
-        <v>3669.2</v>
+        <v>474.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6219.4</v>
+        <v>3808.1</v>
       </c>
       <c r="H11" t="n">
-        <v>5047.3</v>
+        <v>2025</v>
       </c>
       <c r="I11" t="n">
-        <v>8101.9</v>
+        <v>1670.8</v>
       </c>
       <c r="J11" t="n">
-        <v>8054.4</v>
+        <v>6368.3</v>
       </c>
       <c r="K11" t="n">
-        <v>594.7</v>
+        <v>3991</v>
       </c>
       <c r="L11" t="n">
-        <v>5481.4</v>
+        <v>5194.9</v>
       </c>
       <c r="M11" t="n">
-        <v>5777.3</v>
+        <v>7545.9</v>
       </c>
     </row>
     <row r="12">
@@ -919,40 +919,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1118</v>
+        <v>4207.2</v>
       </c>
       <c r="C12" t="n">
-        <v>5211.9</v>
+        <v>2028.7</v>
       </c>
       <c r="D12" t="n">
-        <v>3542.4</v>
+        <v>7602.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4968.7</v>
+        <v>4602.1</v>
       </c>
       <c r="F12" t="n">
-        <v>6721.1</v>
+        <v>6303.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5647.5</v>
+        <v>6832.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5530.7</v>
+        <v>5774.2</v>
       </c>
       <c r="I12" t="n">
-        <v>7022.8</v>
+        <v>7838.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2011.3</v>
+        <v>4018.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4789.1</v>
+        <v>1925.4</v>
       </c>
       <c r="L12" t="n">
-        <v>2720.1</v>
+        <v>3392.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4193.1</v>
+        <v>213.6</v>
       </c>
     </row>
   </sheetData>
